--- a/Lakehouse map/Bronze_layer.xlsx
+++ b/Lakehouse map/Bronze_layer.xlsx
@@ -65,7 +65,7 @@
     <t>zone_type</t>
   </si>
   <si>
-    <t>Geographic aggregation level detected (Districts, Municipalities, GAU).</t>
+    <t>Geographic hierarchy level(Districts, Municipalities, GAU).</t>
   </si>
   <si>
     <t>year</t>
